--- a/updates/Migration_to_Semantic_Device_Identifiers-Mapping.xlsx
+++ b/updates/Migration_to_Semantic_Device_Identifiers-Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rawma\Dropbox\mobile\re-mapping device codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDA4989-068A-4DF9-BADB-C923A3DDB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE1C730-1B37-4B86-A31B-5026DF4DD89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17220" yWindow="5250" windowWidth="40710" windowHeight="22350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="630">
   <si>
     <t>A-1</t>
   </si>
@@ -1960,6 +1960,9 @@
   </si>
   <si>
     <t>A permanent snapshot URL preserving the device page before changes were implemented, for archival and historical reference.</t>
+  </si>
+  <si>
+    <t>(also at https://doi.org/10.64393/balagha.semantic.ID)</t>
   </si>
 </sst>
 </file>
@@ -2435,7 +2438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624EA10D-530A-4D63-89DF-AE1E238EE93A}">
-  <dimension ref="A8:A50"/>
+  <dimension ref="A8:A51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="112.42578125" customWidth="1"/>
@@ -2471,121 +2474,130 @@
         <v>611</v>
       </c>
     </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>629</v>
+      </c>
+    </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+    <row r="22" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>619</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A16" r:id="rId1" xr:uid="{26135577-6B93-4C98-B065-E2056A3544F9}"/>
     <hyperlink ref="A8" r:id="rId2" xr:uid="{F727E66D-C6E5-45CE-9202-4DCE1CE858BF}"/>
+    <hyperlink ref="A17" r:id="rId3" display="https://doi.org/10.64393/balagha.semantic.ID" xr:uid="{94CEE45D-D854-4E91-BE80-81BDD4B3236B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
